--- a/Team-Data/2012-13/3-6-2012-13.xlsx
+++ b/Team-Data/2012-13/3-6-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,28 +728,28 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F2" t="n">
         <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
       </c>
       <c r="I2" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J2" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.463</v>
+        <v>0.462</v>
       </c>
       <c r="L2" t="n">
         <v>9</v>
@@ -691,16 +758,16 @@
         <v>23.7</v>
       </c>
       <c r="N2" t="n">
-        <v>0.382</v>
+        <v>0.38</v>
       </c>
       <c r="O2" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="P2" t="n">
         <v>19.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.705</v>
+        <v>0.706</v>
       </c>
       <c r="R2" t="n">
         <v>9.300000000000001</v>
@@ -709,10 +776,10 @@
         <v>31.4</v>
       </c>
       <c r="T2" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="U2" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="V2" t="n">
         <v>15</v>
@@ -733,22 +800,22 @@
         <v>18.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>97.59999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF2" t="n">
         <v>9</v>
       </c>
       <c r="AG2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
         <v>11</v>
@@ -766,7 +833,7 @@
         <v>3</v>
       </c>
       <c r="AM2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN2" t="n">
         <v>5</v>
@@ -778,7 +845,7 @@
         <v>28</v>
       </c>
       <c r="AQ2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR2" t="n">
         <v>27</v>
@@ -790,7 +857,7 @@
         <v>25</v>
       </c>
       <c r="AU2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV2" t="n">
         <v>17</v>
@@ -811,7 +878,7 @@
         <v>25</v>
       </c>
       <c r="BB2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -843,58 +910,58 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E3" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F3" t="n">
         <v>27</v>
       </c>
       <c r="G3" t="n">
-        <v>0.55</v>
+        <v>0.542</v>
       </c>
       <c r="H3" t="n">
         <v>49.3</v>
       </c>
       <c r="I3" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="J3" t="n">
         <v>80.59999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L3" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="M3" t="n">
         <v>16.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.347</v>
+        <v>0.346</v>
       </c>
       <c r="O3" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="P3" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="R3" t="n">
         <v>8.4</v>
       </c>
       <c r="S3" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T3" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="U3" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="V3" t="n">
         <v>14.5</v>
@@ -906,28 +973,28 @@
         <v>4.3</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>96.09999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG3" t="n">
         <v>13</v>
@@ -936,10 +1003,10 @@
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK3" t="n">
         <v>9</v>
@@ -951,22 +1018,22 @@
         <v>26</v>
       </c>
       <c r="AN3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AP3" t="n">
         <v>22</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>24</v>
       </c>
       <c r="AQ3" t="n">
         <v>7</v>
       </c>
       <c r="AR3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT3" t="n">
         <v>28</v>
@@ -978,10 +1045,10 @@
         <v>10</v>
       </c>
       <c r="AW3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY3" t="n">
         <v>10</v>
@@ -996,7 +1063,7 @@
         <v>18</v>
       </c>
       <c r="BC3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F4" t="n">
         <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>0.574</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
@@ -1043,19 +1110,19 @@
         <v>35</v>
       </c>
       <c r="J4" t="n">
-        <v>79.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="K4" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L4" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M4" t="n">
         <v>21.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0.361</v>
+        <v>0.358</v>
       </c>
       <c r="O4" t="n">
         <v>17.3</v>
@@ -1064,43 +1131,43 @@
         <v>23.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.738</v>
+        <v>0.737</v>
       </c>
       <c r="R4" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>29.8</v>
       </c>
       <c r="T4" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U4" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V4" t="n">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="W4" t="n">
         <v>7.1</v>
       </c>
       <c r="X4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z4" t="n">
         <v>18.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB4" t="n">
         <v>95</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="AD4" t="n">
         <v>12</v>
@@ -1124,7 +1191,7 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AL4" t="n">
         <v>9</v>
@@ -1136,7 +1203,7 @@
         <v>14</v>
       </c>
       <c r="AO4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP4" t="n">
         <v>9</v>
@@ -1145,28 +1212,28 @@
         <v>21</v>
       </c>
       <c r="AR4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU4" t="n">
         <v>28</v>
       </c>
       <c r="AV4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AW4" t="n">
         <v>22</v>
       </c>
       <c r="AX4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ4" t="n">
         <v>3</v>
@@ -1178,7 +1245,7 @@
         <v>19</v>
       </c>
       <c r="BC4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -1207,58 +1274,58 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E5" t="n">
         <v>13</v>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G5" t="n">
-        <v>0.213</v>
+        <v>0.217</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>34.2</v>
+        <v>34.3</v>
       </c>
       <c r="J5" t="n">
-        <v>81.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.418</v>
+        <v>0.419</v>
       </c>
       <c r="L5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="M5" t="n">
         <v>16.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.34</v>
+        <v>0.342</v>
       </c>
       <c r="O5" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.749</v>
+      </c>
+      <c r="R5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="U5" t="n">
         <v>18.9</v>
-      </c>
-      <c r="P5" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.748</v>
-      </c>
-      <c r="R5" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="S5" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>19</v>
       </c>
       <c r="V5" t="n">
         <v>14</v>
@@ -1267,7 +1334,7 @@
         <v>7.1</v>
       </c>
       <c r="X5" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Y5" t="n">
         <v>7.5</v>
@@ -1276,13 +1343,13 @@
         <v>19.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>93</v>
+        <v>93.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-10.3</v>
+        <v>-10.1</v>
       </c>
       <c r="AD5" t="n">
         <v>12</v>
@@ -1297,13 +1364,13 @@
         <v>30</v>
       </c>
       <c r="AH5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI5" t="n">
         <v>30</v>
       </c>
       <c r="AJ5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
@@ -1315,10 +1382,10 @@
         <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AP5" t="n">
         <v>5</v>
@@ -1327,13 +1394,13 @@
         <v>18</v>
       </c>
       <c r="AR5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS5" t="n">
         <v>27</v>
       </c>
       <c r="AT5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AU5" t="n">
         <v>30</v>
@@ -1354,7 +1421,7 @@
         <v>11</v>
       </c>
       <c r="BA5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB5" t="n">
         <v>27</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -1389,64 +1456,64 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6" t="n">
         <v>34</v>
       </c>
       <c r="F6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>48.3</v>
       </c>
       <c r="I6" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="J6" t="n">
-        <v>81.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.436</v>
+        <v>0.437</v>
       </c>
       <c r="L6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="M6" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="N6" t="n">
-        <v>0.346</v>
+        <v>0.343</v>
       </c>
       <c r="O6" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="P6" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.783</v>
+        <v>0.781</v>
       </c>
       <c r="R6" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="S6" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="T6" t="n">
-        <v>43.3</v>
+        <v>43.4</v>
       </c>
       <c r="U6" t="n">
         <v>23</v>
       </c>
       <c r="V6" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W6" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X6" t="n">
         <v>5.6</v>
@@ -1455,28 +1522,28 @@
         <v>5.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>92.5</v>
+        <v>92.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="AD6" t="n">
         <v>12</v>
       </c>
       <c r="AE6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AH6" t="n">
         <v>21</v>
@@ -1485,10 +1552,10 @@
         <v>25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL6" t="n">
         <v>29</v>
@@ -1506,25 +1573,25 @@
         <v>21</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR6" t="n">
         <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU6" t="n">
         <v>8</v>
       </c>
       <c r="AV6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX6" t="n">
         <v>9</v>
@@ -1536,7 +1603,7 @@
         <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB6" t="n">
         <v>28</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F7" t="n">
         <v>40</v>
       </c>
       <c r="G7" t="n">
-        <v>0.344</v>
+        <v>0.333</v>
       </c>
       <c r="H7" t="n">
         <v>48.2</v>
@@ -1592,34 +1659,34 @@
         <v>84.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.434</v>
+        <v>0.435</v>
       </c>
       <c r="L7" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="M7" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="N7" t="n">
-        <v>0.354</v>
+        <v>0.353</v>
       </c>
       <c r="O7" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P7" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="R7" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="S7" t="n">
-        <v>28.2</v>
+        <v>28.1</v>
       </c>
       <c r="T7" t="n">
-        <v>40.8</v>
+        <v>40.6</v>
       </c>
       <c r="U7" t="n">
         <v>20.6</v>
@@ -1631,73 +1698,73 @@
         <v>8.1</v>
       </c>
       <c r="X7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Y7" t="n">
         <v>7.2</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>97.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>-3.4</v>
+        <v>-3.5</v>
       </c>
       <c r="AD7" t="n">
         <v>12</v>
       </c>
       <c r="AE7" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AF7" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AG7" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AH7" t="n">
         <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL7" t="n">
         <v>15</v>
       </c>
       <c r="AM7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO7" t="n">
         <v>10</v>
       </c>
       <c r="AP7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ7" t="n">
         <v>14</v>
       </c>
       <c r="AR7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS7" t="n">
         <v>30</v>
       </c>
       <c r="AT7" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AU7" t="n">
         <v>25</v>
@@ -1709,22 +1776,22 @@
         <v>14</v>
       </c>
       <c r="AX7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY7" t="n">
         <v>29</v>
       </c>
       <c r="AZ7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -1753,61 +1820,61 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F8" t="n">
         <v>33</v>
       </c>
       <c r="G8" t="n">
-        <v>0.45</v>
+        <v>0.441</v>
       </c>
       <c r="H8" t="n">
         <v>48.8</v>
       </c>
       <c r="I8" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="J8" t="n">
-        <v>84.2</v>
+        <v>84.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L8" t="n">
         <v>7.3</v>
       </c>
       <c r="M8" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.368</v>
+        <v>0.367</v>
       </c>
       <c r="O8" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P8" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="Q8" t="n">
         <v>0.794</v>
       </c>
       <c r="R8" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="S8" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="T8" t="n">
-        <v>42.1</v>
+        <v>42.3</v>
       </c>
       <c r="U8" t="n">
-        <v>22.9</v>
+        <v>22.6</v>
       </c>
       <c r="V8" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W8" t="n">
         <v>8</v>
@@ -1825,13 +1892,13 @@
         <v>19.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>101.2</v>
+        <v>101</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1.5</v>
+        <v>-1.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE8" t="n">
         <v>19</v>
@@ -1849,10 +1916,10 @@
         <v>7</v>
       </c>
       <c r="AJ8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL8" t="n">
         <v>13</v>
@@ -1876,16 +1943,16 @@
         <v>26</v>
       </c>
       <c r="AS8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW8" t="n">
         <v>15</v>
@@ -1903,10 +1970,10 @@
         <v>22</v>
       </c>
       <c r="BB8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>4</v>
       </c>
       <c r="AD9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>5</v>
@@ -2025,7 +2092,7 @@
         <v>6</v>
       </c>
       <c r="AH9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI9" t="n">
         <v>1</v>
@@ -2043,7 +2110,7 @@
         <v>18</v>
       </c>
       <c r="AN9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO9" t="n">
         <v>7</v>
@@ -2058,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="AS9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT9" t="n">
         <v>2</v>
       </c>
       <c r="AU9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW9" t="n">
         <v>2</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -2117,25 +2184,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E10" t="n">
         <v>23</v>
       </c>
       <c r="F10" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G10" t="n">
-        <v>0.365</v>
+        <v>0.371</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="J10" t="n">
-        <v>81.3</v>
+        <v>81.5</v>
       </c>
       <c r="K10" t="n">
         <v>0.444</v>
@@ -2144,34 +2211,34 @@
         <v>6.1</v>
       </c>
       <c r="M10" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="N10" t="n">
         <v>0.362</v>
       </c>
       <c r="O10" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="P10" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="Q10" t="n">
         <v>0.694</v>
       </c>
       <c r="R10" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S10" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="T10" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="U10" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V10" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W10" t="n">
         <v>6.9</v>
@@ -2183,22 +2250,22 @@
         <v>5.7</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>94.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.4</v>
+        <v>-3.3</v>
       </c>
       <c r="AD10" t="n">
         <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF10" t="n">
         <v>23</v>
@@ -2237,7 +2304,7 @@
         <v>28</v>
       </c>
       <c r="AR10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS10" t="n">
         <v>14</v>
@@ -2252,7 +2319,7 @@
         <v>22</v>
       </c>
       <c r="AW10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX10" t="n">
         <v>12</v>
@@ -2264,10 +2331,10 @@
         <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC10" t="n">
         <v>22</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -2299,28 +2366,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F11" t="n">
         <v>27</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
       </c>
       <c r="I11" t="n">
-        <v>37.8</v>
+        <v>38</v>
       </c>
       <c r="J11" t="n">
-        <v>83.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.454</v>
+        <v>0.456</v>
       </c>
       <c r="L11" t="n">
         <v>7.9</v>
@@ -2329,22 +2396,22 @@
         <v>20</v>
       </c>
       <c r="N11" t="n">
-        <v>0.394</v>
+        <v>0.395</v>
       </c>
       <c r="O11" t="n">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="P11" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8</v>
+        <v>0.798</v>
       </c>
       <c r="R11" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S11" t="n">
-        <v>33.8</v>
+        <v>33.7</v>
       </c>
       <c r="T11" t="n">
         <v>44.7</v>
@@ -2365,28 +2432,28 @@
         <v>5.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="AA11" t="n">
         <v>19.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>101</v>
+        <v>101.3</v>
       </c>
       <c r="AC11" t="n">
         <v>-0.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
         <v>9</v>
       </c>
       <c r="AF11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
         <v>18</v>
@@ -2398,13 +2465,13 @@
         <v>8</v>
       </c>
       <c r="AK11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL11" t="n">
         <v>8</v>
       </c>
       <c r="AM11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN11" t="n">
         <v>1</v>
@@ -2413,28 +2480,28 @@
         <v>11</v>
       </c>
       <c r="AP11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ11" t="n">
         <v>2</v>
       </c>
       <c r="AR11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS11" t="n">
         <v>1</v>
       </c>
       <c r="AT11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV11" t="n">
         <v>26</v>
       </c>
       <c r="AW11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX11" t="n">
         <v>27</v>
@@ -2446,10 +2513,10 @@
         <v>29</v>
       </c>
       <c r="BA11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC11" t="n">
         <v>16</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E12" t="n">
         <v>33</v>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G12" t="n">
-        <v>0.532</v>
+        <v>0.541</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
       </c>
       <c r="I12" t="n">
-        <v>38.7</v>
+        <v>38.8</v>
       </c>
       <c r="J12" t="n">
-        <v>83</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K12" t="n">
         <v>0.466</v>
@@ -2508,61 +2575,61 @@
         <v>10.6</v>
       </c>
       <c r="M12" t="n">
-        <v>28.8</v>
+        <v>28.7</v>
       </c>
       <c r="N12" t="n">
         <v>0.37</v>
       </c>
       <c r="O12" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="P12" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="Q12" t="n">
         <v>0.753</v>
       </c>
       <c r="R12" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S12" t="n">
         <v>32</v>
       </c>
       <c r="T12" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="U12" t="n">
         <v>23.5</v>
       </c>
       <c r="V12" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="W12" t="n">
         <v>8.5</v>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Z12" t="n">
         <v>20.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB12" t="n">
         <v>107</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF12" t="n">
         <v>14</v>
@@ -2592,7 +2659,7 @@
         <v>8</v>
       </c>
       <c r="AO12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AP12" t="n">
         <v>6</v>
@@ -2607,16 +2674,16 @@
         <v>8</v>
       </c>
       <c r="AT12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV12" t="n">
         <v>30</v>
       </c>
       <c r="AW12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX12" t="n">
         <v>28</v>
@@ -2628,7 +2695,7 @@
         <v>17</v>
       </c>
       <c r="BA12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB12" t="n">
         <v>1</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E13" t="n">
         <v>38</v>
       </c>
       <c r="F13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G13" t="n">
-        <v>0.623</v>
+        <v>0.633</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
@@ -2681,28 +2748,28 @@
         <v>35</v>
       </c>
       <c r="J13" t="n">
-        <v>80.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="K13" t="n">
-        <v>0.434</v>
+        <v>0.435</v>
       </c>
       <c r="L13" t="n">
         <v>6.9</v>
       </c>
       <c r="M13" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0.352</v>
+        <v>0.355</v>
       </c>
       <c r="O13" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="P13" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.743</v>
+        <v>0.742</v>
       </c>
       <c r="R13" t="n">
         <v>12.8</v>
@@ -2711,10 +2778,10 @@
         <v>33</v>
       </c>
       <c r="T13" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
       <c r="U13" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="V13" t="n">
         <v>15.2</v>
@@ -2723,22 +2790,22 @@
         <v>7.1</v>
       </c>
       <c r="X13" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="Y13" t="n">
         <v>5.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB13" t="n">
-        <v>93.7</v>
+        <v>94</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AD13" t="n">
         <v>12</v>
@@ -2747,10 +2814,10 @@
         <v>7</v>
       </c>
       <c r="AF13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH13" t="n">
         <v>12</v>
@@ -2759,10 +2826,10 @@
         <v>28</v>
       </c>
       <c r="AJ13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL13" t="n">
         <v>16</v>
@@ -2771,19 +2838,19 @@
         <v>15</v>
       </c>
       <c r="AN13" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AO13" t="n">
         <v>16</v>
       </c>
       <c r="AP13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AQ13" t="n">
         <v>20</v>
       </c>
       <c r="AR13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS13" t="n">
         <v>4</v>
@@ -2792,10 +2859,10 @@
         <v>1</v>
       </c>
       <c r="AU13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW13" t="n">
         <v>24</v>
@@ -2804,7 +2871,7 @@
         <v>3</v>
       </c>
       <c r="AY13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ13" t="n">
         <v>16</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -2845,43 +2912,43 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F14" t="n">
         <v>19</v>
       </c>
       <c r="G14" t="n">
-        <v>0.698</v>
+        <v>0.694</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="J14" t="n">
-        <v>80.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.476</v>
+        <v>0.475</v>
       </c>
       <c r="L14" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M14" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0.357</v>
+        <v>0.356</v>
       </c>
       <c r="O14" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="P14" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="Q14" t="n">
         <v>0.706</v>
@@ -2896,10 +2963,10 @@
         <v>41.7</v>
       </c>
       <c r="U14" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="V14" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W14" t="n">
         <v>9.9</v>
@@ -2908,25 +2975,25 @@
         <v>5.9</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>100.8</v>
+        <v>100.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF14" t="n">
         <v>4</v>
@@ -2962,7 +3029,7 @@
         <v>8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR14" t="n">
         <v>13</v>
@@ -2974,10 +3041,10 @@
         <v>17</v>
       </c>
       <c r="AU14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -2992,7 +3059,7 @@
         <v>23</v>
       </c>
       <c r="BA14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB14" t="n">
         <v>9</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E15" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F15" t="n">
         <v>31</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5</v>
+        <v>0.492</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
@@ -3045,13 +3112,13 @@
         <v>37.3</v>
       </c>
       <c r="J15" t="n">
-        <v>81</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M15" t="n">
         <v>24.2</v>
@@ -3063,25 +3130,25 @@
         <v>19</v>
       </c>
       <c r="P15" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="R15" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S15" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="T15" t="n">
-        <v>44.5</v>
+        <v>44.7</v>
       </c>
       <c r="U15" t="n">
         <v>22</v>
       </c>
       <c r="V15" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W15" t="n">
         <v>7.1</v>
@@ -3090,7 +3157,7 @@
         <v>5.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z15" t="n">
         <v>18.4</v>
@@ -3099,13 +3166,13 @@
         <v>23</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.4</v>
+        <v>102.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
         <v>16</v>
@@ -3135,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO15" t="n">
         <v>3</v>
@@ -3153,7 +3220,7 @@
         <v>3</v>
       </c>
       <c r="AT15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU15" t="n">
         <v>16</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -3209,22 +3276,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F16" t="n">
         <v>19</v>
       </c>
       <c r="G16" t="n">
-        <v>0.678</v>
+        <v>0.672</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J16" t="n">
         <v>82.2</v>
@@ -3233,7 +3300,7 @@
         <v>0.441</v>
       </c>
       <c r="L16" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="M16" t="n">
         <v>13.7</v>
@@ -3242,31 +3309,31 @@
         <v>0.346</v>
       </c>
       <c r="O16" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P16" t="n">
         <v>20.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.777</v>
+        <v>0.779</v>
       </c>
       <c r="R16" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="S16" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T16" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U16" t="n">
         <v>21.2</v>
       </c>
       <c r="V16" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W16" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X16" t="n">
         <v>5.2</v>
@@ -3284,13 +3351,13 @@
         <v>93.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD16" t="n">
         <v>25</v>
       </c>
       <c r="AE16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF16" t="n">
         <v>4</v>
@@ -3305,7 +3372,7 @@
         <v>23</v>
       </c>
       <c r="AJ16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AK16" t="n">
         <v>22</v>
@@ -3317,13 +3384,13 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ16" t="n">
         <v>8</v>
@@ -3335,28 +3402,28 @@
         <v>26</v>
       </c>
       <c r="AT16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU16" t="n">
         <v>23</v>
       </c>
       <c r="AV16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AW16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX16" t="n">
         <v>14</v>
       </c>
       <c r="AY16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ16" t="n">
         <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB16" t="n">
         <v>26</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -3391,46 +3458,46 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E17" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F17" t="n">
         <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>0.763</v>
+        <v>0.759</v>
       </c>
       <c r="H17" t="n">
         <v>48.7</v>
       </c>
       <c r="I17" t="n">
-        <v>38.9</v>
+        <v>39.1</v>
       </c>
       <c r="J17" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="K17" t="n">
-        <v>0.495</v>
+        <v>0.496</v>
       </c>
       <c r="L17" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.387</v>
+        <v>0.391</v>
       </c>
       <c r="O17" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P17" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.764</v>
+        <v>0.761</v>
       </c>
       <c r="R17" t="n">
         <v>8.4</v>
@@ -3439,10 +3506,10 @@
         <v>30.3</v>
       </c>
       <c r="T17" t="n">
-        <v>38.7</v>
+        <v>38.8</v>
       </c>
       <c r="U17" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="V17" t="n">
         <v>13.5</v>
@@ -3451,7 +3518,7 @@
         <v>8.699999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y17" t="n">
         <v>3.3</v>
@@ -3460,13 +3527,13 @@
         <v>19.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>103.5</v>
+        <v>103.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="AD17" t="n">
         <v>25</v>
@@ -3499,19 +3566,19 @@
         <v>8</v>
       </c>
       <c r="AN17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ17" t="n">
         <v>15</v>
       </c>
       <c r="AR17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS17" t="n">
         <v>19</v>
@@ -3538,7 +3605,7 @@
         <v>12</v>
       </c>
       <c r="BA17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BB17" t="n">
         <v>5</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E18" t="n">
         <v>30</v>
       </c>
       <c r="F18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G18" t="n">
-        <v>0.508</v>
+        <v>0.517</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
@@ -3591,70 +3658,70 @@
         <v>38</v>
       </c>
       <c r="J18" t="n">
-        <v>87</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="K18" t="n">
         <v>0.437</v>
       </c>
       <c r="L18" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M18" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.354</v>
+        <v>0.351</v>
       </c>
       <c r="O18" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="P18" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.736</v>
+        <v>0.735</v>
       </c>
       <c r="R18" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="S18" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T18" t="n">
-        <v>43.6</v>
+        <v>43.8</v>
       </c>
       <c r="U18" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V18" t="n">
         <v>14.4</v>
       </c>
       <c r="W18" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X18" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB18" t="n">
         <v>98.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1</v>
+        <v>-0.7</v>
       </c>
       <c r="AD18" t="n">
         <v>25</v>
       </c>
       <c r="AE18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF18" t="n">
         <v>14</v>
@@ -3672,16 +3739,16 @@
         <v>1</v>
       </c>
       <c r="AK18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM18" t="n">
         <v>19</v>
       </c>
       <c r="AN18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO18" t="n">
         <v>24</v>
@@ -3693,7 +3760,7 @@
         <v>23</v>
       </c>
       <c r="AR18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS18" t="n">
         <v>13</v>
@@ -3702,28 +3769,28 @@
         <v>5</v>
       </c>
       <c r="AU18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV18" t="n">
         <v>9</v>
       </c>
       <c r="AW18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX18" t="n">
         <v>2</v>
       </c>
       <c r="AY18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ18" t="n">
         <v>9</v>
       </c>
       <c r="BA18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC18" t="n">
         <v>17</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -3755,25 +3822,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F19" t="n">
         <v>37</v>
       </c>
       <c r="G19" t="n">
-        <v>0.362</v>
+        <v>0.351</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="J19" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K19" t="n">
         <v>0.433</v>
@@ -3782,64 +3849,64 @@
         <v>5.3</v>
       </c>
       <c r="M19" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="N19" t="n">
         <v>0.297</v>
       </c>
       <c r="O19" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="P19" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.732</v>
+        <v>0.733</v>
       </c>
       <c r="R19" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="S19" t="n">
-        <v>30.3</v>
+        <v>30.4</v>
       </c>
       <c r="T19" t="n">
-        <v>43</v>
+        <v>43.2</v>
       </c>
       <c r="U19" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="V19" t="n">
         <v>15.2</v>
       </c>
       <c r="W19" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y19" t="n">
         <v>6.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>94.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.8</v>
+        <v>-3</v>
       </c>
       <c r="AD19" t="n">
         <v>29</v>
       </c>
       <c r="AE19" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AF19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG19" t="n">
         <v>23</v>
@@ -3878,25 +3945,25 @@
         <v>5</v>
       </c>
       <c r="AS19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU19" t="n">
         <v>18</v>
       </c>
       <c r="AV19" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ19" t="n">
         <v>5</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E20" t="n">
         <v>21</v>
       </c>
       <c r="F20" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G20" t="n">
-        <v>0.339</v>
+        <v>0.344</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3955,7 +4022,7 @@
         <v>36.3</v>
       </c>
       <c r="J20" t="n">
-        <v>80.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K20" t="n">
         <v>0.451</v>
@@ -3964,73 +4031,73 @@
         <v>6.8</v>
       </c>
       <c r="M20" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="N20" t="n">
         <v>0.371</v>
       </c>
       <c r="O20" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="P20" t="n">
         <v>19.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R20" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S20" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="T20" t="n">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="U20" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V20" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W20" t="n">
         <v>6.3</v>
       </c>
       <c r="X20" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y20" t="n">
         <v>6.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA20" t="n">
         <v>18.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>94.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3.5</v>
+        <v>-3.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
         <v>23</v>
       </c>
       <c r="AF20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH20" t="n">
         <v>22</v>
       </c>
       <c r="AI20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ20" t="n">
         <v>27</v>
@@ -4054,13 +4121,13 @@
         <v>26</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT20" t="n">
         <v>22</v>
@@ -4069,7 +4136,7 @@
         <v>22</v>
       </c>
       <c r="AV20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW20" t="n">
         <v>29</v>
@@ -4078,19 +4145,19 @@
         <v>8</v>
       </c>
       <c r="AY20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA20" t="n">
         <v>27</v>
       </c>
       <c r="BB20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BC20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -4119,25 +4186,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E21" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F21" t="n">
         <v>21</v>
       </c>
       <c r="G21" t="n">
-        <v>0.638</v>
+        <v>0.632</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
       </c>
       <c r="I21" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J21" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="K21" t="n">
         <v>0.442</v>
@@ -4146,37 +4213,37 @@
         <v>10.8</v>
       </c>
       <c r="M21" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="N21" t="n">
         <v>0.37</v>
       </c>
       <c r="O21" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P21" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.761</v>
+        <v>0.76</v>
       </c>
       <c r="R21" t="n">
         <v>11.2</v>
       </c>
       <c r="S21" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T21" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U21" t="n">
         <v>19.6</v>
       </c>
       <c r="V21" t="n">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="W21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X21" t="n">
         <v>3.8</v>
@@ -4185,16 +4252,16 @@
         <v>3.9</v>
       </c>
       <c r="Z21" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>99.90000000000001</v>
+        <v>100.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD21" t="n">
         <v>29</v>
@@ -4206,16 +4273,16 @@
         <v>6</v>
       </c>
       <c r="AG21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH21" t="n">
         <v>28</v>
       </c>
       <c r="AI21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ21" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AK21" t="n">
         <v>17</v>
@@ -4233,16 +4300,16 @@
         <v>19</v>
       </c>
       <c r="AP21" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AQ21" t="n">
         <v>16</v>
       </c>
       <c r="AR21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT21" t="n">
         <v>21</v>
@@ -4257,7 +4324,7 @@
         <v>13</v>
       </c>
       <c r="AX21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY21" t="n">
         <v>2</v>
@@ -4266,7 +4333,7 @@
         <v>10</v>
       </c>
       <c r="BA21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -4379,10 +4446,10 @@
         <v>9.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AE22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="n">
         <v>3</v>
@@ -4409,7 +4476,7 @@
         <v>14</v>
       </c>
       <c r="AN22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -4427,28 +4494,28 @@
         <v>6</v>
       </c>
       <c r="AT22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU22" t="n">
         <v>17</v>
       </c>
       <c r="AV22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX22" t="n">
         <v>1</v>
       </c>
       <c r="AY22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -4483,25 +4550,25 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E23" t="n">
         <v>17</v>
       </c>
       <c r="F23" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G23" t="n">
-        <v>0.274</v>
+        <v>0.279</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J23" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="K23" t="n">
         <v>0.453</v>
@@ -4510,10 +4577,10 @@
         <v>6.4</v>
       </c>
       <c r="M23" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="N23" t="n">
-        <v>0.332</v>
+        <v>0.335</v>
       </c>
       <c r="O23" t="n">
         <v>12.4</v>
@@ -4522,16 +4589,16 @@
         <v>16.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R23" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S23" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T23" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U23" t="n">
         <v>23.5</v>
@@ -4540,28 +4607,28 @@
         <v>14.6</v>
       </c>
       <c r="W23" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="X23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="AA23" t="n">
         <v>16.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.3</v>
+        <v>94.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>-6.1</v>
+        <v>-6.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4600,7 +4667,7 @@
         <v>30</v>
       </c>
       <c r="AQ23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR23" t="n">
         <v>24</v>
@@ -4615,7 +4682,7 @@
         <v>5</v>
       </c>
       <c r="AV23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW23" t="n">
         <v>30</v>
@@ -4633,7 +4700,7 @@
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC23" t="n">
         <v>28</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -4665,22 +4732,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E24" t="n">
         <v>23</v>
       </c>
       <c r="F24" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G24" t="n">
-        <v>0.383</v>
+        <v>0.39</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J24" t="n">
         <v>84.09999999999999</v>
@@ -4704,7 +4771,7 @@
         <v>16.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.72</v>
+        <v>0.719</v>
       </c>
       <c r="R24" t="n">
         <v>10.9</v>
@@ -4713,46 +4780,46 @@
         <v>30.7</v>
       </c>
       <c r="T24" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U24" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V24" t="n">
         <v>13</v>
       </c>
       <c r="W24" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X24" t="n">
         <v>4.8</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AA24" t="n">
         <v>16.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>92.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>-3.9</v>
+        <v>-3.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF24" t="n">
         <v>20</v>
       </c>
       <c r="AG24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH24" t="n">
         <v>23</v>
@@ -4761,7 +4828,7 @@
         <v>16</v>
       </c>
       <c r="AJ24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK24" t="n">
         <v>23</v>
@@ -4773,7 +4840,7 @@
         <v>23</v>
       </c>
       <c r="AN24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4785,13 +4852,13 @@
         <v>25</v>
       </c>
       <c r="AR24" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AU24" t="n">
         <v>14</v>
@@ -4803,10 +4870,10 @@
         <v>21</v>
       </c>
       <c r="AX24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ24" t="n">
         <v>6</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -4847,46 +4914,46 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E25" t="n">
         <v>21</v>
       </c>
       <c r="F25" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G25" t="n">
-        <v>0.344</v>
+        <v>0.35</v>
       </c>
       <c r="H25" t="n">
         <v>48.4</v>
       </c>
       <c r="I25" t="n">
-        <v>37</v>
+        <v>37.2</v>
       </c>
       <c r="J25" t="n">
-        <v>84</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L25" t="n">
         <v>5.6</v>
       </c>
       <c r="M25" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.327</v>
+        <v>0.328</v>
       </c>
       <c r="O25" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="P25" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.743</v>
+        <v>0.746</v>
       </c>
       <c r="R25" t="n">
         <v>11.5</v>
@@ -4895,16 +4962,16 @@
         <v>30.1</v>
       </c>
       <c r="T25" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="U25" t="n">
         <v>22.2</v>
       </c>
       <c r="V25" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="W25" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X25" t="n">
         <v>5.4</v>
@@ -4919,10 +4986,10 @@
         <v>18.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>94.2</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>-5.5</v>
+        <v>-5.2</v>
       </c>
       <c r="AD25" t="n">
         <v>12</v>
@@ -4937,16 +5004,16 @@
         <v>24</v>
       </c>
       <c r="AH25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI25" t="n">
         <v>13</v>
       </c>
       <c r="AJ25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK25" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL25" t="n">
         <v>27</v>
@@ -4970,16 +5037,16 @@
         <v>14</v>
       </c>
       <c r="AS25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU25" t="n">
         <v>15</v>
       </c>
       <c r="AV25" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AW25" t="n">
         <v>17</v>
@@ -4997,7 +5064,7 @@
         <v>28</v>
       </c>
       <c r="BB25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BC25" t="n">
         <v>27</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -5029,34 +5096,34 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
         <v>28</v>
       </c>
       <c r="F26" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G26" t="n">
-        <v>0.467</v>
+        <v>0.475</v>
       </c>
       <c r="H26" t="n">
         <v>48.6</v>
       </c>
       <c r="I26" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J26" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="K26" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L26" t="n">
         <v>8.1</v>
       </c>
       <c r="M26" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="N26" t="n">
         <v>0.342</v>
@@ -5065,25 +5132,25 @@
         <v>16.3</v>
       </c>
       <c r="P26" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.772</v>
+        <v>0.776</v>
       </c>
       <c r="R26" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S26" t="n">
         <v>30.4</v>
       </c>
       <c r="T26" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="U26" t="n">
         <v>21.6</v>
       </c>
       <c r="V26" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W26" t="n">
         <v>6.9</v>
@@ -5098,22 +5165,22 @@
         <v>18.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.40000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.3</v>
+        <v>-2.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
       </c>
       <c r="AF26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG26" t="n">
         <v>18</v>
@@ -5122,10 +5189,10 @@
         <v>6</v>
       </c>
       <c r="AI26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ26" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AK26" t="n">
         <v>15</v>
@@ -5134,37 +5201,37 @@
         <v>7</v>
       </c>
       <c r="AM26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN26" t="n">
         <v>25</v>
       </c>
       <c r="AO26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ26" t="n">
         <v>9</v>
       </c>
       <c r="AR26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS26" t="n">
         <v>18</v>
       </c>
-      <c r="AS26" t="n">
-        <v>17</v>
-      </c>
       <c r="AT26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU26" t="n">
         <v>21</v>
       </c>
       <c r="AV26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AW26" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AX26" t="n">
         <v>21</v>
@@ -5179,7 +5246,7 @@
         <v>23</v>
       </c>
       <c r="BB26" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BC26" t="n">
         <v>20</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E27" t="n">
         <v>21</v>
       </c>
       <c r="F27" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G27" t="n">
-        <v>0.333</v>
+        <v>0.339</v>
       </c>
       <c r="H27" t="n">
         <v>48.5</v>
@@ -5232,43 +5299,43 @@
         <v>83.59999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L27" t="n">
         <v>7.1</v>
       </c>
       <c r="M27" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N27" t="n">
         <v>0.366</v>
       </c>
       <c r="O27" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="P27" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q27" t="n">
         <v>0.766</v>
       </c>
       <c r="R27" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S27" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="T27" t="n">
         <v>40.5</v>
       </c>
       <c r="U27" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V27" t="n">
         <v>15.1</v>
       </c>
       <c r="W27" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="X27" t="n">
         <v>4.3</v>
@@ -5280,10 +5347,10 @@
         <v>21.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.5</v>
+        <v>98.7</v>
       </c>
       <c r="AC27" t="n">
         <v>-6.4</v>
@@ -5298,7 +5365,7 @@
         <v>28</v>
       </c>
       <c r="AG27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH27" t="n">
         <v>13</v>
@@ -5310,7 +5377,7 @@
         <v>7</v>
       </c>
       <c r="AK27" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL27" t="n">
         <v>14</v>
@@ -5337,31 +5404,31 @@
         <v>29</v>
       </c>
       <c r="AT27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY27" t="n">
         <v>27</v>
       </c>
       <c r="AZ27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA27" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BB27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BC27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E28" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F28" t="n">
         <v>14</v>
       </c>
       <c r="G28" t="n">
-        <v>0.774</v>
+        <v>0.77</v>
       </c>
       <c r="H28" t="n">
         <v>48.6</v>
@@ -5411,7 +5478,7 @@
         <v>39.6</v>
       </c>
       <c r="J28" t="n">
-        <v>81.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="K28" t="n">
         <v>0.488</v>
@@ -5420,16 +5487,16 @@
         <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="N28" t="n">
-        <v>0.383</v>
+        <v>0.381</v>
       </c>
       <c r="O28" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P28" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="Q28" t="n">
         <v>0.788</v>
@@ -5438,16 +5505,16 @@
         <v>7.9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.4</v>
+        <v>33.2</v>
       </c>
       <c r="T28" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="U28" t="n">
         <v>25.3</v>
       </c>
       <c r="V28" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W28" t="n">
         <v>8.800000000000001</v>
@@ -5456,22 +5523,22 @@
         <v>5.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>104.7</v>
+        <v>104.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5489,7 +5556,7 @@
         <v>2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5519,7 +5586,7 @@
         <v>2</v>
       </c>
       <c r="AT28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
@@ -5528,13 +5595,13 @@
         <v>12</v>
       </c>
       <c r="AW28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX28" t="n">
         <v>13</v>
       </c>
       <c r="AY28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -5575,46 +5642,46 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F29" t="n">
         <v>38</v>
       </c>
       <c r="G29" t="n">
-        <v>0.387</v>
+        <v>0.377</v>
       </c>
       <c r="H29" t="n">
         <v>48.9</v>
       </c>
       <c r="I29" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J29" t="n">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="K29" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L29" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M29" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="N29" t="n">
-        <v>0.351</v>
+        <v>0.349</v>
       </c>
       <c r="O29" t="n">
         <v>17.6</v>
       </c>
       <c r="P29" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.782</v>
+        <v>0.781</v>
       </c>
       <c r="R29" t="n">
         <v>10.9</v>
@@ -5629,7 +5696,7 @@
         <v>21.8</v>
       </c>
       <c r="V29" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="W29" t="n">
         <v>7.4</v>
@@ -5641,7 +5708,7 @@
         <v>5.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AA29" t="n">
         <v>20</v>
@@ -5650,10 +5717,10 @@
         <v>97.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.4</v>
+        <v>-1.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
         <v>20</v>
@@ -5662,7 +5729,7 @@
         <v>22</v>
       </c>
       <c r="AG29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH29" t="n">
         <v>2</v>
@@ -5674,7 +5741,7 @@
         <v>13</v>
       </c>
       <c r="AK29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL29" t="n">
         <v>11</v>
@@ -5692,10 +5759,10 @@
         <v>15</v>
       </c>
       <c r="AQ29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS29" t="n">
         <v>28</v>
@@ -5710,10 +5777,10 @@
         <v>3</v>
       </c>
       <c r="AW29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY29" t="n">
         <v>16</v>
@@ -5722,13 +5789,13 @@
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB29" t="n">
         <v>16</v>
       </c>
       <c r="BC29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E30" t="n">
         <v>32</v>
       </c>
       <c r="F30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G30" t="n">
-        <v>0.525</v>
+        <v>0.533</v>
       </c>
       <c r="H30" t="n">
         <v>48.6</v>
@@ -5775,7 +5842,7 @@
         <v>37</v>
       </c>
       <c r="J30" t="n">
-        <v>82.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K30" t="n">
         <v>0.451</v>
@@ -5787,28 +5854,28 @@
         <v>16.6</v>
       </c>
       <c r="N30" t="n">
-        <v>0.362</v>
+        <v>0.359</v>
       </c>
       <c r="O30" t="n">
         <v>18.6</v>
       </c>
       <c r="P30" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.767</v>
+        <v>0.766</v>
       </c>
       <c r="R30" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S30" t="n">
         <v>30</v>
       </c>
       <c r="T30" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="U30" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V30" t="n">
         <v>15</v>
@@ -5817,16 +5884,16 @@
         <v>8.300000000000001</v>
       </c>
       <c r="X30" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Z30" t="n">
         <v>21.6</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB30" t="n">
         <v>98.7</v>
@@ -5838,7 +5905,7 @@
         <v>12</v>
       </c>
       <c r="AE30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF30" t="n">
         <v>14</v>
@@ -5850,10 +5917,10 @@
         <v>7</v>
       </c>
       <c r="AI30" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AJ30" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AK30" t="n">
         <v>14</v>
@@ -5865,7 +5932,7 @@
         <v>27</v>
       </c>
       <c r="AN30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO30" t="n">
         <v>6</v>
@@ -5877,7 +5944,7 @@
         <v>12</v>
       </c>
       <c r="AR30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS30" t="n">
         <v>23</v>
@@ -5886,19 +5953,19 @@
         <v>13</v>
       </c>
       <c r="AU30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV30" t="n">
         <v>19</v>
       </c>
       <c r="AW30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX30" t="n">
         <v>5</v>
       </c>
       <c r="AY30" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AZ30" t="n">
         <v>28</v>
@@ -5907,7 +5974,7 @@
         <v>9</v>
       </c>
       <c r="BB30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC30" t="n">
         <v>15</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
@@ -5939,25 +6006,25 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E31" t="n">
         <v>19</v>
       </c>
       <c r="F31" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G31" t="n">
-        <v>0.322</v>
+        <v>0.328</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="J31" t="n">
-        <v>81.8</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K31" t="n">
         <v>0.43</v>
@@ -5969,34 +6036,34 @@
         <v>18.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O31" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="P31" t="n">
         <v>20</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.738</v>
+        <v>0.737</v>
       </c>
       <c r="R31" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S31" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="T31" t="n">
         <v>43.4</v>
       </c>
       <c r="U31" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V31" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="W31" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X31" t="n">
         <v>4.7</v>
@@ -6005,16 +6072,16 @@
         <v>4.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>91.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>-3.5</v>
+        <v>-3.4</v>
       </c>
       <c r="AD31" t="n">
         <v>25</v>
@@ -6035,13 +6102,13 @@
         <v>27</v>
       </c>
       <c r="AJ31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AK31" t="n">
         <v>29</v>
       </c>
       <c r="AL31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM31" t="n">
         <v>20</v>
@@ -6062,28 +6129,28 @@
         <v>23</v>
       </c>
       <c r="AS31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AT31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU31" t="n">
         <v>19</v>
       </c>
       <c r="AV31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW31" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AX31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY31" t="n">
         <v>13</v>
       </c>
       <c r="AZ31" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA31" t="n">
         <v>26</v>
@@ -6092,7 +6159,7 @@
         <v>30</v>
       </c>
       <c r="BC31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-6-2012-13</t>
+          <t>2013-03-06</t>
         </is>
       </c>
     </row>
